--- a/samples/예시데이터_관리대장.xlsx
+++ b/samples/예시데이터_관리대장.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:R11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,6 +445,15 @@
       <c r="O1" t="str">
         <v>메모</v>
       </c>
+      <c r="P1" t="str">
+        <v>PO 납기</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>OC 번호</v>
+      </c>
+      <c r="R1" t="str">
+        <v>항차 진행</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -492,6 +501,15 @@
       <c r="O2" t="str">
         <v/>
       </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v>4/13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -539,6 +557,15 @@
       <c r="O3" t="str">
         <v/>
       </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>4/13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -586,6 +613,15 @@
       <c r="O4" t="str">
         <v/>
       </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>4/13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -633,6 +669,15 @@
       <c r="O5" t="str">
         <v/>
       </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>3/13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -680,6 +725,15 @@
       <c r="O6" t="str">
         <v/>
       </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v>3/13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -727,6 +781,15 @@
       <c r="O7" t="str">
         <v/>
       </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v>1/13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -774,6 +837,15 @@
       <c r="O8" t="str">
         <v/>
       </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v>1/13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -821,6 +893,15 @@
       <c r="O9" t="str">
         <v/>
       </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v>1/13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -868,6 +949,15 @@
       <c r="O10" t="str">
         <v/>
       </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v>3/13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -915,10 +1005,19 @@
       <c r="O11" t="str">
         <v/>
       </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v>1/13</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/예시데이터_관리대장.xlsx
+++ b/samples/예시데이터_관리대장.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:S11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,6 +452,9 @@
         <v>OC 번호</v>
       </c>
       <c r="R1" t="str">
+        <v>EXW 일정(품번별)</v>
+      </c>
+      <c r="S1" t="str">
         <v>항차 진행</v>
       </c>
     </row>
@@ -508,6 +511,9 @@
         <v/>
       </c>
       <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
         <v>4/13</v>
       </c>
     </row>
@@ -564,6 +570,9 @@
         <v/>
       </c>
       <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
         <v>4/13</v>
       </c>
     </row>
@@ -620,6 +629,9 @@
         <v/>
       </c>
       <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
         <v>4/13</v>
       </c>
     </row>
@@ -676,6 +688,9 @@
         <v/>
       </c>
       <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
         <v>3/13</v>
       </c>
     </row>
@@ -732,6 +747,9 @@
         <v/>
       </c>
       <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
         <v>3/13</v>
       </c>
     </row>
@@ -788,6 +806,9 @@
         <v/>
       </c>
       <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
         <v>1/13</v>
       </c>
     </row>
@@ -844,6 +865,9 @@
         <v/>
       </c>
       <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
         <v>1/13</v>
       </c>
     </row>
@@ -900,6 +924,9 @@
         <v/>
       </c>
       <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
         <v>1/13</v>
       </c>
     </row>
@@ -956,6 +983,9 @@
         <v/>
       </c>
       <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
         <v>3/13</v>
       </c>
     </row>
@@ -1012,12 +1042,15 @@
         <v/>
       </c>
       <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
         <v>1/13</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/예시데이터_관리대장.xlsx
+++ b/samples/예시데이터_관리대장.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:V11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,6 +457,15 @@
       <c r="S1" t="str">
         <v>항차 진행</v>
       </c>
+      <c r="T1" t="str">
+        <v>B/L 번호</v>
+      </c>
+      <c r="U1" t="str">
+        <v>ETA</v>
+      </c>
+      <c r="V1" t="str">
+        <v>항차등록일</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -516,6 +525,15 @@
       <c r="S2" t="str">
         <v>4/13</v>
       </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -575,6 +593,15 @@
       <c r="S3" t="str">
         <v>4/13</v>
       </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -634,6 +661,15 @@
       <c r="S4" t="str">
         <v>4/13</v>
       </c>
+      <c r="T4" t="str">
+        <v>GMAO26090077</v>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -693,6 +729,15 @@
       <c r="S5" t="str">
         <v>3/13</v>
       </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -752,6 +797,15 @@
       <c r="S6" t="str">
         <v>3/13</v>
       </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -811,6 +865,15 @@
       <c r="S7" t="str">
         <v>1/13</v>
       </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -870,6 +933,15 @@
       <c r="S8" t="str">
         <v>1/13</v>
       </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -929,6 +1001,15 @@
       <c r="S9" t="str">
         <v>1/13</v>
       </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -988,6 +1069,15 @@
       <c r="S10" t="str">
         <v>3/13</v>
       </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1047,10 +1137,19 @@
       <c r="S11" t="str">
         <v>1/13</v>
       </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V11"/>
   </ignoredErrors>
 </worksheet>
 </file>